--- a/Assets/Data/DataTable/03_Buff_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buff_Table.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B7D636A-C0D8-416F-91F7-DDBF67736DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5421204E-7C94-460A-92C2-09AB760FC638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,8 +460,7 @@
 21: 신성 속성 과부하 계수
 22: 피해 배율
 23: 받는 피해 배율
-24: SP 소모량 증가
-25: 도발</t>
+24: SP 소모량 증가</t>
         </r>
       </text>
     </comment>
@@ -470,7 +469,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="88">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -793,14 +792,6 @@
   </si>
   <si>
     <t>enum:BUFF_TYPE:NONE</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1025</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -3739,7 +3730,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.25" style="30" bestFit="1" customWidth="1"/>
@@ -3751,7 +3742,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B1"/>
       <c r="C1"/>
@@ -3798,7 +3789,7 @@
     </row>
     <row r="4" spans="1:12" s="27" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B4" s="26" t="s">
         <v>59</v>
@@ -3810,7 +3801,7 @@
         <v>63</v>
       </c>
       <c r="E4" s="26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F4" s="26"/>
       <c r="L4"/>
@@ -4274,131 +4265,12 @@
       <c r="F28" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="25">
-        <f t="shared" si="1"/>
-        <v>30001025</v>
-      </c>
-      <c r="B29" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" s="32">
-        <v>0</v>
-      </c>
-      <c r="D29" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="E29" s="24">
-        <v>25</v>
-      </c>
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="24"/>
       <c r="F29" s="34"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="30">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="30">
-        <f t="shared" ref="A31:A47" si="2">(B31*1000000) + (C32*10000) + D31</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A33" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A35" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A36" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A37" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A38" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A39" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A40" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A41" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A42" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A43" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A44" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A45" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A46" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A47" s="30">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Assets/Data/DataTable/03_Buff_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buff_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5421204E-7C94-460A-92C2-09AB760FC638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DCA63A-0DB9-4629-8337-7325F91A54AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,7 +460,9 @@
 21: 신성 속성 과부하 계수
 22: 피해 배율
 23: 받는 피해 배율
-24: SP 소모량 증가</t>
+24: SP 소모량 증가
+25: 매턴 데미지
+26: 매턴 체력 회복</t>
         </r>
       </text>
     </comment>
@@ -469,7 +471,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -804,6 +806,18 @@
   </si>
   <si>
     <t>Table_Buff</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1010</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3730,7 +3744,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.25" style="30" bestFit="1" customWidth="1"/>
@@ -3988,8 +4002,8 @@
       <c r="C14" s="32">
         <v>0</v>
       </c>
-      <c r="D14" s="25">
-        <v>1010</v>
+      <c r="D14" s="25" t="s">
+        <v>90</v>
       </c>
       <c r="E14" s="24">
         <v>10</v>
@@ -4114,7 +4128,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
-        <f t="shared" ref="A21:A30" si="1">(B21*1000000) + (C21*10000) + D21</f>
+        <f t="shared" ref="A21:A28" si="1">(B21*1000000) + (C21*10000) + D21</f>
         <v>30001017</v>
       </c>
       <c r="B21" s="25">
@@ -4265,16 +4279,46 @@
       <c r="F28" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="24"/>
+      <c r="A29" s="25">
+        <f t="shared" ref="A29:A30" si="2">(B29*1000000) + (C29*10000) + D29</f>
+        <v>30001025</v>
+      </c>
+      <c r="B29" s="25">
+        <v>30</v>
+      </c>
+      <c r="C29" s="32">
+        <v>0</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="24">
+        <v>25</v>
+      </c>
       <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="25">
+        <f t="shared" si="2"/>
+        <v>30001026</v>
+      </c>
+      <c r="B30" s="25">
+        <v>30</v>
+      </c>
+      <c r="C30" s="32">
+        <v>0</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="24">
+        <v>26</v>
+      </c>
+      <c r="F30" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C1:C1048576 C1:C4">
+  <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -4285,7 +4329,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C30 C32:C1048576" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C1048576 C5:C30" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/Data/DataTable/03_Buff_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buff_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DCA63A-0DB9-4629-8337-7325F91A54AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE02B83-750A-4029-8703-83B8001462E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -462,7 +462,10 @@
 23: 받는 피해 배율
 24: SP 소모량 증가
 25: 매턴 데미지
-26: 매턴 체력 회복</t>
+26: 매턴 체력 회복
+27: 기절
+28: 이상
+29: 침묵</t>
         </r>
       </text>
     </comment>
@@ -471,7 +474,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -818,6 +821,19 @@
   </si>
   <si>
     <t>1010</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1027</t>
+  </si>
+  <si>
+    <t>1028</t>
+  </si>
+  <si>
+    <t>1029</t>
+  </si>
+  <si>
+    <t>30</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3744,7 +3760,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.25" style="30" bestFit="1" customWidth="1"/>
@@ -4299,7 +4315,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="25">
-        <f t="shared" si="2"/>
+        <f>(B30*1000000) + (C30*10000) + D30</f>
         <v>30001026</v>
       </c>
       <c r="B30" s="25">
@@ -4315,6 +4331,63 @@
         <v>26</v>
       </c>
       <c r="F30" s="34"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="25">
+        <f t="shared" ref="A31:A33" si="3">(B31*1000000) + (C31*10000) + D31</f>
+        <v>30001027</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C31" s="32">
+        <v>0</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="E31" s="24">
+        <v>27</v>
+      </c>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="25">
+        <f t="shared" si="3"/>
+        <v>30001028</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="32">
+        <v>0</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>92</v>
+      </c>
+      <c r="E32" s="24">
+        <v>28</v>
+      </c>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="25">
+        <f t="shared" si="3"/>
+        <v>30001029</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C33" s="32">
+        <v>0</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="24">
+        <v>29</v>
+      </c>
+      <c r="F33" s="34"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4329,7 +4402,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C32:C1048576 C5:C30" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C1048576" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
       <formula1>"0,1"</formula1>
     </dataValidation>
   </dataValidations>

--- a/Assets/Data/DataTable/03_Buff_Table.xlsx
+++ b/Assets/Data/DataTable/03_Buff_Table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\Astrocat-2DSFProject\Assets\Data\DataTable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE02B83-750A-4029-8703-83B8001462E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ADD01CA-FA4E-4251-9FE6-E2F049CE3E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -451,21 +451,26 @@
 12: 중력 속성 게이지 효율 계수
 13: 공허 속성 게이지 효율 계수
 14: 신성 속성 게이지 효율 계수
-15: 속성 게이지 저항 계수
-16: 물리 속성 과부하 계수
-17: 화염 속성 과부하 계수
-18: 방사능 속성 과부하 계수
-19: 중력 속성 과부하 계수
-20: 공허 속성 과부하 계수
-21: 신성 속성 과부하 계수
-22: 피해 배율
-23: 받는 피해 배율
-24: SP 소모량 증가
-25: 매턴 데미지
-26: 매턴 체력 회복
-27: 기절
-28: 이상
-29: 침묵</t>
+15: 물리 속성 게이지 저항 계수
+16: 화염 속성 게이지 저항 계수
+17: 방사능 속성 게이지 저항 계수
+18: 중력 속성 게이지 저항 계수
+19: 공허 속성 게이지 저항 계수
+20: 신성 속성 게이지 저항 계수
+21: 물리 속성 과부하 계수
+22: 화염 속성 과부하 계수
+23: 방사능 속성 과부하 계수
+24: 중력 속성 과부하 계수
+25: 공허 속성 과부하 계수
+26: 신성 속성 과부하 계수
+27: 피해 배율
+28: 받는 피해 배율
+29: SP 소모량 증가
+30: 매턴 데미지
+31: 매턴 체력 회복
+32: 기절
+33: 이상
+34: 침묵</t>
         </r>
       </text>
     </comment>
@@ -474,7 +479,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="100">
   <si>
     <t>Hero_ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -835,6 +840,21 @@
   <si>
     <t>30</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1030</t>
+  </si>
+  <si>
+    <t>1031</t>
+  </si>
+  <si>
+    <t>1032</t>
+  </si>
+  <si>
+    <t>1033</t>
+  </si>
+  <si>
+    <t>1034</t>
   </si>
 </sst>
 </file>
@@ -3760,7 +3780,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4201226D-AF20-433D-BB3C-B7FD91A16A54}">
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="10.25" style="30" bestFit="1" customWidth="1"/>
@@ -4296,7 +4316,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="25">
-        <f t="shared" ref="A29:A30" si="2">(B29*1000000) + (C29*10000) + D29</f>
+        <f t="shared" ref="A29" si="2">(B29*1000000) + (C29*10000) + D29</f>
         <v>30001025</v>
       </c>
       <c r="B29" s="25">
@@ -4334,7 +4354,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="25">
-        <f t="shared" ref="A31:A33" si="3">(B31*1000000) + (C31*10000) + D31</f>
+        <f t="shared" ref="A31" si="3">(B31*1000000) + (C31*10000) + D31</f>
         <v>30001027</v>
       </c>
       <c r="B31" s="25" t="s">
@@ -4353,7 +4373,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="25">
-        <f t="shared" si="3"/>
+        <f>(B32*1000000) + (C32*10000) + D32</f>
         <v>30001028</v>
       </c>
       <c r="B32" s="25" t="s">
@@ -4372,7 +4392,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="25">
-        <f t="shared" si="3"/>
+        <f>(B33*1000000) + (C33*10000) + D33</f>
         <v>30001029</v>
       </c>
       <c r="B33" s="25" t="s">
@@ -4388,6 +4408,96 @@
         <v>29</v>
       </c>
       <c r="F33" s="34"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="25">
+        <f t="shared" ref="A34:A38" si="4">(B34*1000000) + (C34*10000) + D34</f>
+        <v>30001030</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="32">
+        <v>0</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" s="24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="25">
+        <f t="shared" si="4"/>
+        <v>30001031</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C35" s="32">
+        <v>0</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="E35" s="24">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="25">
+        <f t="shared" si="4"/>
+        <v>30001032</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="32">
+        <v>0</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E36" s="24">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="25">
+        <f t="shared" si="4"/>
+        <v>30001033</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C37" s="32">
+        <v>0</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="24">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="25">
+        <f t="shared" si="4"/>
+        <v>30001034</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="C38" s="32">
+        <v>0</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="E38" s="24">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4401,7 +4511,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:C1048576" xr:uid="{2E37FA97-16C9-4CD8-BF57-92BA0291CA83}">
       <formula1>"0,1"</formula1>
     </dataValidation>
@@ -4411,7 +4521,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8D44D287-4A0D-4E30-B02E-F978C229F037}">
           <x14:formula1>
             <xm:f>'!Logic'!$A$5:$A$19</xm:f>
